--- a/idecba/masa_salarial.xlsx
+++ b/idecba/masa_salarial.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20745" windowHeight="2145"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25455" windowHeight="8745"/>
   </bookViews>
   <sheets>
     <sheet name="ee_industria_masa_salarial" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="58">
   <si>
     <t xml:space="preserve">Año </t>
   </si>
@@ -225,7 +225,10 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Masa salarial por rama de actividad (Índice base octubre 2001 = 100). Ciudad de Buenos Aires. Octubre 2001/Diciembre 2025</t>
+    <t>Masa salarial por rama de actividad (Índice base octubre 2001 = 100). Ciudad de Buenos Aires. Octubre 2001/Marzo 2026</t>
+  </si>
+  <si>
+    <t>2026*</t>
   </si>
 </sst>
 </file>
@@ -1400,14 +1403,47 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1420,39 +1456,6 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="45" xfId="35" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1810,7 +1813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CD297"/>
+  <dimension ref="A1:CD300"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="7" customWidth="1"/>
@@ -1818,45 +1821,45 @@
     <col min="3" max="12" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="83"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="76"/>
     </row>
     <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="73"/>
-      <c r="B3" s="75"/>
+      <c r="A3" s="84"/>
+      <c r="B3" s="86"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1889,7 +1892,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="76">
+      <c r="A4" s="77">
         <v>2001</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -1927,7 +1930,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="70"/>
+      <c r="A5" s="72"/>
       <c r="B5" s="9" t="s">
         <v>14</v>
       </c>
@@ -1963,7 +1966,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
+      <c r="A6" s="73"/>
       <c r="B6" s="10" t="s">
         <v>15</v>
       </c>
@@ -1999,7 +2002,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="70">
+      <c r="A7" s="72">
         <v>2002</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -2037,7 +2040,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="70"/>
+      <c r="A8" s="72"/>
       <c r="B8" s="9" t="s">
         <v>17</v>
       </c>
@@ -2073,7 +2076,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="70"/>
+      <c r="A9" s="72"/>
       <c r="B9" s="9" t="s">
         <v>18</v>
       </c>
@@ -2109,7 +2112,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
+      <c r="A10" s="72"/>
       <c r="B10" s="9" t="s">
         <v>19</v>
       </c>
@@ -2145,7 +2148,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="70"/>
+      <c r="A11" s="72"/>
       <c r="B11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2181,7 +2184,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
+      <c r="A12" s="72"/>
       <c r="B12" s="9" t="s">
         <v>21</v>
       </c>
@@ -2217,7 +2220,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="70"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="9" t="s">
         <v>22</v>
       </c>
@@ -2253,7 +2256,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="70"/>
+      <c r="A14" s="72"/>
       <c r="B14" s="9" t="s">
         <v>23</v>
       </c>
@@ -2289,7 +2292,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="70"/>
+      <c r="A15" s="72"/>
       <c r="B15" s="9" t="s">
         <v>24</v>
       </c>
@@ -2325,7 +2328,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="70"/>
+      <c r="A16" s="72"/>
       <c r="B16" s="9" t="s">
         <v>13</v>
       </c>
@@ -2361,7 +2364,7 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="70"/>
+      <c r="A17" s="72"/>
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
@@ -2397,7 +2400,7 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="71"/>
+      <c r="A18" s="73"/>
       <c r="B18" s="10" t="s">
         <v>15</v>
       </c>
@@ -2433,7 +2436,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="70">
+      <c r="A19" s="72">
         <v>2003</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -2471,7 +2474,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="70"/>
+      <c r="A20" s="72"/>
       <c r="B20" s="9" t="s">
         <v>17</v>
       </c>
@@ -2507,7 +2510,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="70"/>
+      <c r="A21" s="72"/>
       <c r="B21" s="9" t="s">
         <v>18</v>
       </c>
@@ -2543,7 +2546,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="70"/>
+      <c r="A22" s="72"/>
       <c r="B22" s="9" t="s">
         <v>19</v>
       </c>
@@ -2579,7 +2582,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="70"/>
+      <c r="A23" s="72"/>
       <c r="B23" s="9" t="s">
         <v>20</v>
       </c>
@@ -2615,7 +2618,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="70"/>
+      <c r="A24" s="72"/>
       <c r="B24" s="9" t="s">
         <v>21</v>
       </c>
@@ -2651,7 +2654,7 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="70"/>
+      <c r="A25" s="72"/>
       <c r="B25" s="9" t="s">
         <v>22</v>
       </c>
@@ -2687,7 +2690,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="70"/>
+      <c r="A26" s="72"/>
       <c r="B26" s="9" t="s">
         <v>23</v>
       </c>
@@ -2723,7 +2726,7 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="70"/>
+      <c r="A27" s="72"/>
       <c r="B27" s="9" t="s">
         <v>24</v>
       </c>
@@ -2759,7 +2762,7 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="70"/>
+      <c r="A28" s="72"/>
       <c r="B28" s="9" t="s">
         <v>13</v>
       </c>
@@ -2795,7 +2798,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="70"/>
+      <c r="A29" s="72"/>
       <c r="B29" s="9" t="s">
         <v>14</v>
       </c>
@@ -2831,7 +2834,7 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="71"/>
+      <c r="A30" s="73"/>
       <c r="B30" s="10" t="s">
         <v>15</v>
       </c>
@@ -2867,7 +2870,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="70">
+      <c r="A31" s="72">
         <v>2004</v>
       </c>
       <c r="B31" s="9" t="s">
@@ -2905,7 +2908,7 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="70"/>
+      <c r="A32" s="72"/>
       <c r="B32" s="9" t="s">
         <v>17</v>
       </c>
@@ -2941,7 +2944,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="70"/>
+      <c r="A33" s="72"/>
       <c r="B33" s="9" t="s">
         <v>18</v>
       </c>
@@ -2977,7 +2980,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="70"/>
+      <c r="A34" s="72"/>
       <c r="B34" s="9" t="s">
         <v>19</v>
       </c>
@@ -3013,7 +3016,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="70"/>
+      <c r="A35" s="72"/>
       <c r="B35" s="9" t="s">
         <v>20</v>
       </c>
@@ -3049,7 +3052,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="70"/>
+      <c r="A36" s="72"/>
       <c r="B36" s="9" t="s">
         <v>21</v>
       </c>
@@ -3085,7 +3088,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="70"/>
+      <c r="A37" s="72"/>
       <c r="B37" s="9" t="s">
         <v>22</v>
       </c>
@@ -3121,7 +3124,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="70"/>
+      <c r="A38" s="72"/>
       <c r="B38" s="9" t="s">
         <v>23</v>
       </c>
@@ -3157,7 +3160,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="70"/>
+      <c r="A39" s="72"/>
       <c r="B39" s="9" t="s">
         <v>24</v>
       </c>
@@ -3193,7 +3196,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="70"/>
+      <c r="A40" s="72"/>
       <c r="B40" s="9" t="s">
         <v>13</v>
       </c>
@@ -3229,7 +3232,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="70"/>
+      <c r="A41" s="72"/>
       <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
@@ -3265,7 +3268,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="71"/>
+      <c r="A42" s="73"/>
       <c r="B42" s="10" t="s">
         <v>15</v>
       </c>
@@ -3301,7 +3304,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="70">
+      <c r="A43" s="72">
         <v>2005</v>
       </c>
       <c r="B43" s="9" t="s">
@@ -3339,7 +3342,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="70"/>
+      <c r="A44" s="72"/>
       <c r="B44" s="9" t="s">
         <v>17</v>
       </c>
@@ -3375,7 +3378,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="70"/>
+      <c r="A45" s="72"/>
       <c r="B45" s="9" t="s">
         <v>18</v>
       </c>
@@ -3411,7 +3414,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="70"/>
+      <c r="A46" s="72"/>
       <c r="B46" s="9" t="s">
         <v>19</v>
       </c>
@@ -3447,7 +3450,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="70"/>
+      <c r="A47" s="72"/>
       <c r="B47" s="9" t="s">
         <v>20</v>
       </c>
@@ -3483,7 +3486,7 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="70"/>
+      <c r="A48" s="72"/>
       <c r="B48" s="9" t="s">
         <v>21</v>
       </c>
@@ -3519,7 +3522,7 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="70"/>
+      <c r="A49" s="72"/>
       <c r="B49" s="9" t="s">
         <v>22</v>
       </c>
@@ -3555,7 +3558,7 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="70"/>
+      <c r="A50" s="72"/>
       <c r="B50" s="9" t="s">
         <v>23</v>
       </c>
@@ -3591,7 +3594,7 @@
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="70"/>
+      <c r="A51" s="72"/>
       <c r="B51" s="9" t="s">
         <v>24</v>
       </c>
@@ -3627,7 +3630,7 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="70"/>
+      <c r="A52" s="72"/>
       <c r="B52" s="9" t="s">
         <v>13</v>
       </c>
@@ -3663,7 +3666,7 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="70"/>
+      <c r="A53" s="72"/>
       <c r="B53" s="9" t="s">
         <v>14</v>
       </c>
@@ -3699,7 +3702,7 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="71"/>
+      <c r="A54" s="73"/>
       <c r="B54" s="10" t="s">
         <v>15</v>
       </c>
@@ -3735,7 +3738,7 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="70">
+      <c r="A55" s="72">
         <v>2006</v>
       </c>
       <c r="B55" s="9" t="s">
@@ -3773,7 +3776,7 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="70"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="9" t="s">
         <v>17</v>
       </c>
@@ -3809,7 +3812,7 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="70"/>
+      <c r="A57" s="72"/>
       <c r="B57" s="9" t="s">
         <v>18</v>
       </c>
@@ -3845,7 +3848,7 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="70"/>
+      <c r="A58" s="72"/>
       <c r="B58" s="9" t="s">
         <v>19</v>
       </c>
@@ -3881,7 +3884,7 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="70"/>
+      <c r="A59" s="72"/>
       <c r="B59" s="9" t="s">
         <v>20</v>
       </c>
@@ -3917,7 +3920,7 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="70"/>
+      <c r="A60" s="72"/>
       <c r="B60" s="9" t="s">
         <v>21</v>
       </c>
@@ -3953,7 +3956,7 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="70"/>
+      <c r="A61" s="72"/>
       <c r="B61" s="9" t="s">
         <v>22</v>
       </c>
@@ -3989,7 +3992,7 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="70"/>
+      <c r="A62" s="72"/>
       <c r="B62" s="9" t="s">
         <v>23</v>
       </c>
@@ -4025,7 +4028,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="70"/>
+      <c r="A63" s="72"/>
       <c r="B63" s="9" t="s">
         <v>24</v>
       </c>
@@ -4061,7 +4064,7 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="70"/>
+      <c r="A64" s="72"/>
       <c r="B64" s="9" t="s">
         <v>13</v>
       </c>
@@ -4097,7 +4100,7 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="70"/>
+      <c r="A65" s="72"/>
       <c r="B65" s="9" t="s">
         <v>14</v>
       </c>
@@ -4133,7 +4136,7 @@
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="71"/>
+      <c r="A66" s="73"/>
       <c r="B66" s="10" t="s">
         <v>15</v>
       </c>
@@ -4169,7 +4172,7 @@
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="70">
+      <c r="A67" s="72">
         <v>2007</v>
       </c>
       <c r="B67" s="9" t="s">
@@ -4207,7 +4210,7 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="70"/>
+      <c r="A68" s="72"/>
       <c r="B68" s="9" t="s">
         <v>17</v>
       </c>
@@ -4243,7 +4246,7 @@
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="70"/>
+      <c r="A69" s="72"/>
       <c r="B69" s="9" t="s">
         <v>18</v>
       </c>
@@ -4279,7 +4282,7 @@
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="70"/>
+      <c r="A70" s="72"/>
       <c r="B70" s="9" t="s">
         <v>19</v>
       </c>
@@ -4315,7 +4318,7 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="70"/>
+      <c r="A71" s="72"/>
       <c r="B71" s="9" t="s">
         <v>20</v>
       </c>
@@ -4351,7 +4354,7 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="70"/>
+      <c r="A72" s="72"/>
       <c r="B72" s="9" t="s">
         <v>21</v>
       </c>
@@ -4387,7 +4390,7 @@
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="70"/>
+      <c r="A73" s="72"/>
       <c r="B73" s="9" t="s">
         <v>22</v>
       </c>
@@ -4423,7 +4426,7 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="70"/>
+      <c r="A74" s="72"/>
       <c r="B74" s="9" t="s">
         <v>23</v>
       </c>
@@ -4459,7 +4462,7 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="70"/>
+      <c r="A75" s="72"/>
       <c r="B75" s="9" t="s">
         <v>24</v>
       </c>
@@ -4495,7 +4498,7 @@
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="70"/>
+      <c r="A76" s="72"/>
       <c r="B76" s="9" t="s">
         <v>13</v>
       </c>
@@ -4531,7 +4534,7 @@
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="70"/>
+      <c r="A77" s="72"/>
       <c r="B77" s="9" t="s">
         <v>14</v>
       </c>
@@ -4567,7 +4570,7 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="71"/>
+      <c r="A78" s="73"/>
       <c r="B78" s="10" t="s">
         <v>15</v>
       </c>
@@ -4603,7 +4606,7 @@
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="70">
+      <c r="A79" s="72">
         <v>2008</v>
       </c>
       <c r="B79" s="9" t="s">
@@ -4641,7 +4644,7 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="70"/>
+      <c r="A80" s="72"/>
       <c r="B80" s="9" t="s">
         <v>17</v>
       </c>
@@ -4677,7 +4680,7 @@
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="70"/>
+      <c r="A81" s="72"/>
       <c r="B81" s="9" t="s">
         <v>18</v>
       </c>
@@ -4713,7 +4716,7 @@
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="70"/>
+      <c r="A82" s="72"/>
       <c r="B82" s="9" t="s">
         <v>19</v>
       </c>
@@ -4749,7 +4752,7 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="70"/>
+      <c r="A83" s="72"/>
       <c r="B83" s="9" t="s">
         <v>20</v>
       </c>
@@ -4785,7 +4788,7 @@
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="70"/>
+      <c r="A84" s="72"/>
       <c r="B84" s="9" t="s">
         <v>21</v>
       </c>
@@ -4821,7 +4824,7 @@
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="70"/>
+      <c r="A85" s="72"/>
       <c r="B85" s="9" t="s">
         <v>22</v>
       </c>
@@ -4857,7 +4860,7 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="70"/>
+      <c r="A86" s="72"/>
       <c r="B86" s="9" t="s">
         <v>23</v>
       </c>
@@ -4893,7 +4896,7 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="70"/>
+      <c r="A87" s="72"/>
       <c r="B87" s="9" t="s">
         <v>24</v>
       </c>
@@ -4929,7 +4932,7 @@
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="70"/>
+      <c r="A88" s="72"/>
       <c r="B88" s="9" t="s">
         <v>13</v>
       </c>
@@ -4965,7 +4968,7 @@
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="70"/>
+      <c r="A89" s="72"/>
       <c r="B89" s="9" t="s">
         <v>14</v>
       </c>
@@ -5001,7 +5004,7 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="71"/>
+      <c r="A90" s="73"/>
       <c r="B90" s="10" t="s">
         <v>15</v>
       </c>
@@ -5037,7 +5040,7 @@
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="76">
+      <c r="A91" s="77">
         <v>2009</v>
       </c>
       <c r="B91" s="9" t="s">
@@ -5075,7 +5078,7 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="70"/>
+      <c r="A92" s="72"/>
       <c r="B92" s="9" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5114,7 @@
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="70"/>
+      <c r="A93" s="72"/>
       <c r="B93" s="9" t="s">
         <v>18</v>
       </c>
@@ -5147,7 +5150,7 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="70"/>
+      <c r="A94" s="72"/>
       <c r="B94" s="9" t="s">
         <v>19</v>
       </c>
@@ -5183,7 +5186,7 @@
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="70"/>
+      <c r="A95" s="72"/>
       <c r="B95" s="9" t="s">
         <v>20</v>
       </c>
@@ -5219,7 +5222,7 @@
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="70"/>
+      <c r="A96" s="72"/>
       <c r="B96" s="9" t="s">
         <v>21</v>
       </c>
@@ -5255,7 +5258,7 @@
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="70"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="9" t="s">
         <v>22</v>
       </c>
@@ -5291,7 +5294,7 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="70"/>
+      <c r="A98" s="72"/>
       <c r="B98" s="9" t="s">
         <v>23</v>
       </c>
@@ -5327,7 +5330,7 @@
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="70"/>
+      <c r="A99" s="72"/>
       <c r="B99" s="9" t="s">
         <v>24</v>
       </c>
@@ -5363,7 +5366,7 @@
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="70"/>
+      <c r="A100" s="72"/>
       <c r="B100" s="9" t="s">
         <v>13</v>
       </c>
@@ -5399,7 +5402,7 @@
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="70"/>
+      <c r="A101" s="72"/>
       <c r="B101" s="9" t="s">
         <v>14</v>
       </c>
@@ -5435,7 +5438,7 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="71"/>
+      <c r="A102" s="73"/>
       <c r="B102" s="10" t="s">
         <v>15</v>
       </c>
@@ -5471,7 +5474,7 @@
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="76">
+      <c r="A103" s="77">
         <v>2010</v>
       </c>
       <c r="B103" s="9" t="s">
@@ -5509,7 +5512,7 @@
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="70"/>
+      <c r="A104" s="72"/>
       <c r="B104" s="9" t="s">
         <v>17</v>
       </c>
@@ -5545,7 +5548,7 @@
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="70"/>
+      <c r="A105" s="72"/>
       <c r="B105" s="9" t="s">
         <v>18</v>
       </c>
@@ -5581,7 +5584,7 @@
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="70"/>
+      <c r="A106" s="72"/>
       <c r="B106" s="9" t="s">
         <v>19</v>
       </c>
@@ -5617,7 +5620,7 @@
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="70"/>
+      <c r="A107" s="72"/>
       <c r="B107" s="9" t="s">
         <v>20</v>
       </c>
@@ -5653,7 +5656,7 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="70"/>
+      <c r="A108" s="72"/>
       <c r="B108" s="9" t="s">
         <v>21</v>
       </c>
@@ -5689,7 +5692,7 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="70"/>
+      <c r="A109" s="72"/>
       <c r="B109" s="9" t="s">
         <v>22</v>
       </c>
@@ -5725,7 +5728,7 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="70"/>
+      <c r="A110" s="72"/>
       <c r="B110" s="9" t="s">
         <v>23</v>
       </c>
@@ -5761,7 +5764,7 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="70"/>
+      <c r="A111" s="72"/>
       <c r="B111" s="9" t="s">
         <v>24</v>
       </c>
@@ -5797,7 +5800,7 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="70"/>
+      <c r="A112" s="72"/>
       <c r="B112" s="9" t="s">
         <v>13</v>
       </c>
@@ -5833,7 +5836,7 @@
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="70"/>
+      <c r="A113" s="72"/>
       <c r="B113" s="9" t="s">
         <v>14</v>
       </c>
@@ -5869,7 +5872,7 @@
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="71"/>
+      <c r="A114" s="73"/>
       <c r="B114" s="10" t="s">
         <v>15</v>
       </c>
@@ -5905,7 +5908,7 @@
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="76">
+      <c r="A115" s="77">
         <v>2011</v>
       </c>
       <c r="B115" s="9" t="s">
@@ -5943,7 +5946,7 @@
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="70"/>
+      <c r="A116" s="72"/>
       <c r="B116" s="9" t="s">
         <v>17</v>
       </c>
@@ -5979,7 +5982,7 @@
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="70"/>
+      <c r="A117" s="72"/>
       <c r="B117" s="9" t="s">
         <v>18</v>
       </c>
@@ -6015,7 +6018,7 @@
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="70"/>
+      <c r="A118" s="72"/>
       <c r="B118" s="9" t="s">
         <v>19</v>
       </c>
@@ -6051,7 +6054,7 @@
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="70"/>
+      <c r="A119" s="72"/>
       <c r="B119" s="9" t="s">
         <v>20</v>
       </c>
@@ -6087,7 +6090,7 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="70"/>
+      <c r="A120" s="72"/>
       <c r="B120" s="9" t="s">
         <v>21</v>
       </c>
@@ -6123,7 +6126,7 @@
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="70"/>
+      <c r="A121" s="72"/>
       <c r="B121" s="9" t="s">
         <v>22</v>
       </c>
@@ -6159,7 +6162,7 @@
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="70"/>
+      <c r="A122" s="72"/>
       <c r="B122" s="9" t="s">
         <v>23</v>
       </c>
@@ -6195,7 +6198,7 @@
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="70"/>
+      <c r="A123" s="72"/>
       <c r="B123" s="9" t="s">
         <v>24</v>
       </c>
@@ -6231,7 +6234,7 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="70"/>
+      <c r="A124" s="72"/>
       <c r="B124" s="9" t="s">
         <v>13</v>
       </c>
@@ -6267,7 +6270,7 @@
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="70"/>
+      <c r="A125" s="72"/>
       <c r="B125" s="9" t="s">
         <v>14</v>
       </c>
@@ -6303,7 +6306,7 @@
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="71"/>
+      <c r="A126" s="73"/>
       <c r="B126" s="10" t="s">
         <v>15</v>
       </c>
@@ -6339,7 +6342,7 @@
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="76">
+      <c r="A127" s="77">
         <v>2012</v>
       </c>
       <c r="B127" s="9" t="s">
@@ -6377,7 +6380,7 @@
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="70"/>
+      <c r="A128" s="72"/>
       <c r="B128" s="9" t="s">
         <v>17</v>
       </c>
@@ -6413,7 +6416,7 @@
       </c>
     </row>
     <row r="129" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A129" s="70"/>
+      <c r="A129" s="72"/>
       <c r="B129" s="9" t="s">
         <v>18</v>
       </c>
@@ -6449,7 +6452,7 @@
       </c>
     </row>
     <row r="130" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A130" s="70"/>
+      <c r="A130" s="72"/>
       <c r="B130" s="9" t="s">
         <v>19</v>
       </c>
@@ -6485,7 +6488,7 @@
       </c>
     </row>
     <row r="131" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A131" s="70"/>
+      <c r="A131" s="72"/>
       <c r="B131" s="9" t="s">
         <v>20</v>
       </c>
@@ -6521,7 +6524,7 @@
       </c>
     </row>
     <row r="132" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A132" s="70"/>
+      <c r="A132" s="72"/>
       <c r="B132" s="9" t="s">
         <v>21</v>
       </c>
@@ -6557,7 +6560,7 @@
       </c>
     </row>
     <row r="133" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A133" s="70"/>
+      <c r="A133" s="72"/>
       <c r="B133" s="9" t="s">
         <v>22</v>
       </c>
@@ -6593,7 +6596,7 @@
       </c>
     </row>
     <row r="134" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A134" s="70"/>
+      <c r="A134" s="72"/>
       <c r="B134" s="9" t="s">
         <v>23</v>
       </c>
@@ -6629,7 +6632,7 @@
       </c>
     </row>
     <row r="135" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A135" s="70"/>
+      <c r="A135" s="72"/>
       <c r="B135" s="9" t="s">
         <v>24</v>
       </c>
@@ -6665,7 +6668,7 @@
       </c>
     </row>
     <row r="136" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A136" s="70"/>
+      <c r="A136" s="72"/>
       <c r="B136" s="9" t="s">
         <v>13</v>
       </c>
@@ -6701,7 +6704,7 @@
       </c>
     </row>
     <row r="137" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A137" s="70"/>
+      <c r="A137" s="72"/>
       <c r="B137" s="9" t="s">
         <v>14</v>
       </c>
@@ -6737,7 +6740,7 @@
       </c>
     </row>
     <row r="138" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A138" s="71"/>
+      <c r="A138" s="73"/>
       <c r="B138" s="10" t="s">
         <v>15</v>
       </c>
@@ -6773,7 +6776,7 @@
       </c>
     </row>
     <row r="139" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A139" s="76">
+      <c r="A139" s="77">
         <v>2013</v>
       </c>
       <c r="B139" s="8" t="s">
@@ -6811,7 +6814,7 @@
       </c>
     </row>
     <row r="140" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A140" s="70"/>
+      <c r="A140" s="72"/>
       <c r="B140" s="9" t="s">
         <v>17</v>
       </c>
@@ -6847,7 +6850,7 @@
       </c>
     </row>
     <row r="141" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A141" s="70"/>
+      <c r="A141" s="72"/>
       <c r="B141" s="9" t="s">
         <v>18</v>
       </c>
@@ -6883,7 +6886,7 @@
       </c>
     </row>
     <row r="142" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A142" s="70"/>
+      <c r="A142" s="72"/>
       <c r="B142" s="9" t="s">
         <v>19</v>
       </c>
@@ -6919,7 +6922,7 @@
       </c>
     </row>
     <row r="143" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A143" s="70"/>
+      <c r="A143" s="72"/>
       <c r="B143" s="9" t="s">
         <v>20</v>
       </c>
@@ -6955,7 +6958,7 @@
       </c>
     </row>
     <row r="144" spans="1:82" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="70"/>
+      <c r="A144" s="72"/>
       <c r="B144" s="20" t="s">
         <v>21</v>
       </c>
@@ -7061,7 +7064,7 @@
       <c r="CD144" s="19"/>
     </row>
     <row r="145" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="70"/>
+      <c r="A145" s="72"/>
       <c r="B145" s="9" t="s">
         <v>22</v>
       </c>
@@ -7098,7 +7101,7 @@
       <c r="M145"/>
     </row>
     <row r="146" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="70"/>
+      <c r="A146" s="72"/>
       <c r="B146" s="20" t="s">
         <v>23</v>
       </c>
@@ -7135,7 +7138,7 @@
       <c r="M146"/>
     </row>
     <row r="147" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="70"/>
+      <c r="A147" s="72"/>
       <c r="B147" s="20" t="s">
         <v>25</v>
       </c>
@@ -7172,7 +7175,7 @@
       <c r="M147"/>
     </row>
     <row r="148" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="70"/>
+      <c r="A148" s="72"/>
       <c r="B148" s="20" t="s">
         <v>13</v>
       </c>
@@ -7209,7 +7212,7 @@
       <c r="M148"/>
     </row>
     <row r="149" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="70"/>
+      <c r="A149" s="72"/>
       <c r="B149" s="20" t="s">
         <v>14</v>
       </c>
@@ -7246,7 +7249,7 @@
       <c r="M149"/>
     </row>
     <row r="150" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="71"/>
+      <c r="A150" s="73"/>
       <c r="B150" s="25" t="s">
         <v>15</v>
       </c>
@@ -7283,7 +7286,7 @@
       <c r="M150"/>
     </row>
     <row r="151" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="76">
+      <c r="A151" s="77">
         <v>2014</v>
       </c>
       <c r="B151" s="8" t="s">
@@ -7322,7 +7325,7 @@
       <c r="M151" s="32"/>
     </row>
     <row r="152" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="70"/>
+      <c r="A152" s="72"/>
       <c r="B152" s="9" t="s">
         <v>17</v>
       </c>
@@ -7359,7 +7362,7 @@
       <c r="M152" s="32"/>
     </row>
     <row r="153" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="70"/>
+      <c r="A153" s="72"/>
       <c r="B153" s="9" t="s">
         <v>18</v>
       </c>
@@ -7396,7 +7399,7 @@
       <c r="M153" s="32"/>
     </row>
     <row r="154" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="70"/>
+      <c r="A154" s="72"/>
       <c r="B154" s="9" t="s">
         <v>19</v>
       </c>
@@ -7433,7 +7436,7 @@
       <c r="M154" s="32"/>
     </row>
     <row r="155" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="70"/>
+      <c r="A155" s="72"/>
       <c r="B155" s="9" t="s">
         <v>20</v>
       </c>
@@ -7470,7 +7473,7 @@
       <c r="M155" s="32"/>
     </row>
     <row r="156" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="70"/>
+      <c r="A156" s="72"/>
       <c r="B156" s="9" t="s">
         <v>21</v>
       </c>
@@ -7507,7 +7510,7 @@
       <c r="M156" s="32"/>
     </row>
     <row r="157" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="70"/>
+      <c r="A157" s="72"/>
       <c r="B157" s="9" t="s">
         <v>22</v>
       </c>
@@ -7544,7 +7547,7 @@
       <c r="M157" s="32"/>
     </row>
     <row r="158" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="70"/>
+      <c r="A158" s="72"/>
       <c r="B158" s="9" t="s">
         <v>23</v>
       </c>
@@ -7581,7 +7584,7 @@
       <c r="M158" s="32"/>
     </row>
     <row r="159" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="70"/>
+      <c r="A159" s="72"/>
       <c r="B159" s="9" t="s">
         <v>25</v>
       </c>
@@ -7618,7 +7621,7 @@
       <c r="M159" s="32"/>
     </row>
     <row r="160" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="70"/>
+      <c r="A160" s="72"/>
       <c r="B160" s="9" t="s">
         <v>13</v>
       </c>
@@ -7655,7 +7658,7 @@
       <c r="M160" s="32"/>
     </row>
     <row r="161" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="70"/>
+      <c r="A161" s="72"/>
       <c r="B161" s="9" t="s">
         <v>14</v>
       </c>
@@ -7692,7 +7695,7 @@
       <c r="M161" s="32"/>
     </row>
     <row r="162" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="71"/>
+      <c r="A162" s="73"/>
       <c r="B162" s="10" t="s">
         <v>15</v>
       </c>
@@ -7729,7 +7732,7 @@
       <c r="M162" s="32"/>
     </row>
     <row r="163" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="84">
+      <c r="A163" s="78">
         <v>2015</v>
       </c>
       <c r="B163" s="8" t="s">
@@ -7768,7 +7771,7 @@
       <c r="M163" s="32"/>
     </row>
     <row r="164" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="85"/>
+      <c r="A164" s="79"/>
       <c r="B164" s="9" t="s">
         <v>17</v>
       </c>
@@ -7805,7 +7808,7 @@
       <c r="M164" s="32"/>
     </row>
     <row r="165" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="85"/>
+      <c r="A165" s="79"/>
       <c r="B165" s="20" t="s">
         <v>18</v>
       </c>
@@ -7842,7 +7845,7 @@
       <c r="M165" s="32"/>
     </row>
     <row r="166" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="85"/>
+      <c r="A166" s="79"/>
       <c r="B166" s="9" t="s">
         <v>19</v>
       </c>
@@ -7879,7 +7882,7 @@
       <c r="M166" s="32"/>
     </row>
     <row r="167" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="85"/>
+      <c r="A167" s="79"/>
       <c r="B167" s="9" t="s">
         <v>20</v>
       </c>
@@ -7916,7 +7919,7 @@
       <c r="M167" s="32"/>
     </row>
     <row r="168" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="85"/>
+      <c r="A168" s="79"/>
       <c r="B168" s="9" t="s">
         <v>21</v>
       </c>
@@ -7953,7 +7956,7 @@
       <c r="M168" s="32"/>
     </row>
     <row r="169" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="85"/>
+      <c r="A169" s="79"/>
       <c r="B169" s="9" t="s">
         <v>22</v>
       </c>
@@ -7990,7 +7993,7 @@
       <c r="M169" s="32"/>
     </row>
     <row r="170" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="85"/>
+      <c r="A170" s="79"/>
       <c r="B170" s="9" t="s">
         <v>23</v>
       </c>
@@ -8027,7 +8030,7 @@
       <c r="M170" s="32"/>
     </row>
     <row r="171" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="85"/>
+      <c r="A171" s="79"/>
       <c r="B171" s="9" t="s">
         <v>25</v>
       </c>
@@ -8064,7 +8067,7 @@
       <c r="M171" s="32"/>
     </row>
     <row r="172" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="85"/>
+      <c r="A172" s="79"/>
       <c r="B172" s="9" t="s">
         <v>13</v>
       </c>
@@ -8101,7 +8104,7 @@
       <c r="M172" s="32"/>
     </row>
     <row r="173" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="85"/>
+      <c r="A173" s="79"/>
       <c r="B173" s="9" t="s">
         <v>14</v>
       </c>
@@ -8138,7 +8141,7 @@
       <c r="M173" s="32"/>
     </row>
     <row r="174" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="86"/>
+      <c r="A174" s="80"/>
       <c r="B174" s="37" t="s">
         <v>15</v>
       </c>
@@ -10367,7 +10370,7 @@
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A235" s="79">
+      <c r="A235" s="69">
         <v>2021</v>
       </c>
       <c r="B235" s="8" t="s">
@@ -10405,7 +10408,7 @@
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A236" s="77"/>
+      <c r="A236" s="70"/>
       <c r="B236" s="9" t="s">
         <v>17</v>
       </c>
@@ -10441,7 +10444,7 @@
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A237" s="77"/>
+      <c r="A237" s="70"/>
       <c r="B237" s="9" t="s">
         <v>18</v>
       </c>
@@ -10477,7 +10480,7 @@
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A238" s="77"/>
+      <c r="A238" s="70"/>
       <c r="B238" s="9" t="s">
         <v>19</v>
       </c>
@@ -10513,7 +10516,7 @@
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A239" s="77"/>
+      <c r="A239" s="70"/>
       <c r="B239" s="9" t="s">
         <v>20</v>
       </c>
@@ -10549,7 +10552,7 @@
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A240" s="77"/>
+      <c r="A240" s="70"/>
       <c r="B240" s="9" t="s">
         <v>21</v>
       </c>
@@ -10585,7 +10588,7 @@
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A241" s="77"/>
+      <c r="A241" s="70"/>
       <c r="B241" s="9" t="s">
         <v>22</v>
       </c>
@@ -10621,7 +10624,7 @@
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A242" s="77"/>
+      <c r="A242" s="70"/>
       <c r="B242" s="9" t="s">
         <v>23</v>
       </c>
@@ -10657,7 +10660,7 @@
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A243" s="77"/>
+      <c r="A243" s="70"/>
       <c r="B243" s="9" t="s">
         <v>25</v>
       </c>
@@ -10693,7 +10696,7 @@
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A244" s="77"/>
+      <c r="A244" s="70"/>
       <c r="B244" s="9" t="s">
         <v>13</v>
       </c>
@@ -10729,7 +10732,7 @@
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A245" s="77"/>
+      <c r="A245" s="70"/>
       <c r="B245" s="9" t="s">
         <v>14</v>
       </c>
@@ -10765,7 +10768,7 @@
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A246" s="80"/>
+      <c r="A246" s="71"/>
       <c r="B246" s="10" t="s">
         <v>15</v>
       </c>
@@ -10801,7 +10804,7 @@
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A247" s="79">
+      <c r="A247" s="69">
         <v>2022</v>
       </c>
       <c r="B247" s="8" t="s">
@@ -10839,7 +10842,7 @@
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A248" s="77"/>
+      <c r="A248" s="70"/>
       <c r="B248" s="9" t="s">
         <v>17</v>
       </c>
@@ -10875,7 +10878,7 @@
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A249" s="77"/>
+      <c r="A249" s="70"/>
       <c r="B249" s="9" t="s">
         <v>18</v>
       </c>
@@ -10911,7 +10914,7 @@
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A250" s="77"/>
+      <c r="A250" s="70"/>
       <c r="B250" s="9" t="s">
         <v>19</v>
       </c>
@@ -10947,7 +10950,7 @@
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A251" s="77"/>
+      <c r="A251" s="70"/>
       <c r="B251" s="9" t="s">
         <v>20</v>
       </c>
@@ -10983,7 +10986,7 @@
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A252" s="77"/>
+      <c r="A252" s="70"/>
       <c r="B252" s="9" t="s">
         <v>21</v>
       </c>
@@ -11019,7 +11022,7 @@
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A253" s="77"/>
+      <c r="A253" s="70"/>
       <c r="B253" s="9" t="s">
         <v>22</v>
       </c>
@@ -11055,7 +11058,7 @@
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A254" s="77"/>
+      <c r="A254" s="70"/>
       <c r="B254" s="9" t="s">
         <v>23</v>
       </c>
@@ -11091,7 +11094,7 @@
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A255" s="77"/>
+      <c r="A255" s="70"/>
       <c r="B255" s="9" t="s">
         <v>25</v>
       </c>
@@ -11127,7 +11130,7 @@
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A256" s="77"/>
+      <c r="A256" s="70"/>
       <c r="B256" s="9" t="s">
         <v>13</v>
       </c>
@@ -11163,7 +11166,7 @@
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A257" s="77"/>
+      <c r="A257" s="70"/>
       <c r="B257" s="9" t="s">
         <v>14</v>
       </c>
@@ -11199,7 +11202,7 @@
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A258" s="80"/>
+      <c r="A258" s="71"/>
       <c r="B258" s="10" t="s">
         <v>15</v>
       </c>
@@ -11235,7 +11238,7 @@
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A259" s="79">
+      <c r="A259" s="69">
         <v>2023</v>
       </c>
       <c r="B259" s="8" t="s">
@@ -11273,7 +11276,7 @@
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A260" s="77"/>
+      <c r="A260" s="70"/>
       <c r="B260" s="9" t="s">
         <v>17</v>
       </c>
@@ -11309,7 +11312,7 @@
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A261" s="77"/>
+      <c r="A261" s="70"/>
       <c r="B261" s="9" t="s">
         <v>18</v>
       </c>
@@ -11345,7 +11348,7 @@
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A262" s="77"/>
+      <c r="A262" s="70"/>
       <c r="B262" s="9" t="s">
         <v>19</v>
       </c>
@@ -11381,7 +11384,7 @@
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A263" s="77"/>
+      <c r="A263" s="70"/>
       <c r="B263" s="9" t="s">
         <v>20</v>
       </c>
@@ -11417,7 +11420,7 @@
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A264" s="77"/>
+      <c r="A264" s="70"/>
       <c r="B264" s="9" t="s">
         <v>21</v>
       </c>
@@ -11453,7 +11456,7 @@
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A265" s="77"/>
+      <c r="A265" s="70"/>
       <c r="B265" s="9" t="s">
         <v>22</v>
       </c>
@@ -11489,7 +11492,7 @@
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A266" s="77"/>
+      <c r="A266" s="70"/>
       <c r="B266" s="9" t="s">
         <v>23</v>
       </c>
@@ -11525,7 +11528,7 @@
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A267" s="77"/>
+      <c r="A267" s="70"/>
       <c r="B267" s="9" t="s">
         <v>25</v>
       </c>
@@ -11561,7 +11564,7 @@
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A268" s="77"/>
+      <c r="A268" s="70"/>
       <c r="B268" s="9" t="s">
         <v>13</v>
       </c>
@@ -11597,7 +11600,7 @@
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A269" s="77"/>
+      <c r="A269" s="70"/>
       <c r="B269" s="9" t="s">
         <v>14</v>
       </c>
@@ -11633,7 +11636,7 @@
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A270" s="80"/>
+      <c r="A270" s="71"/>
       <c r="B270" s="10" t="s">
         <v>15</v>
       </c>
@@ -11669,7 +11672,7 @@
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A271" s="79">
+      <c r="A271" s="69">
         <v>2024</v>
       </c>
       <c r="B271" s="8" t="s">
@@ -11707,7 +11710,7 @@
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A272" s="77"/>
+      <c r="A272" s="70"/>
       <c r="B272" s="9" t="s">
         <v>17</v>
       </c>
@@ -11743,7 +11746,7 @@
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A273" s="77"/>
+      <c r="A273" s="70"/>
       <c r="B273" s="9" t="s">
         <v>18</v>
       </c>
@@ -11779,7 +11782,7 @@
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A274" s="77"/>
+      <c r="A274" s="70"/>
       <c r="B274" s="9" t="s">
         <v>19</v>
       </c>
@@ -11815,7 +11818,7 @@
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A275" s="77"/>
+      <c r="A275" s="70"/>
       <c r="B275" s="9" t="s">
         <v>20</v>
       </c>
@@ -11851,7 +11854,7 @@
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A276" s="77"/>
+      <c r="A276" s="70"/>
       <c r="B276" s="9" t="s">
         <v>21</v>
       </c>
@@ -11887,7 +11890,7 @@
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A277" s="77"/>
+      <c r="A277" s="70"/>
       <c r="B277" s="9" t="s">
         <v>22</v>
       </c>
@@ -11923,7 +11926,7 @@
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A278" s="77"/>
+      <c r="A278" s="70"/>
       <c r="B278" s="9" t="s">
         <v>23</v>
       </c>
@@ -11959,7 +11962,7 @@
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A279" s="77"/>
+      <c r="A279" s="70"/>
       <c r="B279" s="9" t="s">
         <v>25</v>
       </c>
@@ -11995,7 +11998,7 @@
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A280" s="77"/>
+      <c r="A280" s="70"/>
       <c r="B280" s="9" t="s">
         <v>13</v>
       </c>
@@ -12031,7 +12034,7 @@
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A281" s="77"/>
+      <c r="A281" s="70"/>
       <c r="B281" s="9" t="s">
         <v>14</v>
       </c>
@@ -12067,7 +12070,7 @@
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A282" s="80"/>
+      <c r="A282" s="71"/>
       <c r="B282" s="10" t="s">
         <v>15</v>
       </c>
@@ -12103,45 +12106,45 @@
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A283" s="77" t="s">
+      <c r="A283" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="B283" s="9" t="s">
+      <c r="B283" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C283" s="27">
+      <c r="C283" s="33">
         <v>117735.24377247637</v>
       </c>
-      <c r="D283" s="13">
+      <c r="D283" s="23">
         <v>89341.579799038591</v>
       </c>
-      <c r="E283" s="21">
+      <c r="E283" s="34">
         <v>48668.636466741962</v>
       </c>
-      <c r="F283" s="13">
+      <c r="F283" s="23">
         <v>40930.086831321169</v>
       </c>
-      <c r="G283" s="21">
+      <c r="G283" s="34">
         <v>176899.53968858783</v>
       </c>
-      <c r="H283" s="13">
+      <c r="H283" s="23">
         <v>125256.440691415</v>
       </c>
-      <c r="I283" s="21">
+      <c r="I283" s="34">
         <v>90564.255863922954</v>
       </c>
-      <c r="J283" s="13">
+      <c r="J283" s="23">
         <v>85704.820506668868</v>
       </c>
-      <c r="K283" s="36">
+      <c r="K283" s="59">
         <v>133139.81832006978</v>
       </c>
-      <c r="L283" s="35">
+      <c r="L283" s="60">
         <v>47228.848667404978</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A284" s="77"/>
+      <c r="A284" s="70"/>
       <c r="B284" s="9" t="s">
         <v>17</v>
       </c>
@@ -12177,7 +12180,7 @@
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A285" s="77"/>
+      <c r="A285" s="70"/>
       <c r="B285" s="9" t="s">
         <v>18</v>
       </c>
@@ -12213,7 +12216,7 @@
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A286" s="77"/>
+      <c r="A286" s="70"/>
       <c r="B286" s="9" t="s">
         <v>19</v>
       </c>
@@ -12249,7 +12252,7 @@
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A287" s="77"/>
+      <c r="A287" s="70"/>
       <c r="B287" s="9" t="s">
         <v>20</v>
       </c>
@@ -12285,7 +12288,7 @@
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A288" s="77"/>
+      <c r="A288" s="70"/>
       <c r="B288" s="9" t="s">
         <v>21</v>
       </c>
@@ -12321,7 +12324,7 @@
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A289" s="77"/>
+      <c r="A289" s="70"/>
       <c r="B289" s="9" t="s">
         <v>22</v>
       </c>
@@ -12357,7 +12360,7 @@
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A290" s="77"/>
+      <c r="A290" s="70"/>
       <c r="B290" s="9" t="s">
         <v>23</v>
       </c>
@@ -12393,7 +12396,7 @@
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A291" s="77"/>
+      <c r="A291" s="70"/>
       <c r="B291" s="9" t="s">
         <v>25</v>
       </c>
@@ -12429,7 +12432,7 @@
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A292" s="77"/>
+      <c r="A292" s="70"/>
       <c r="B292" s="9" t="s">
         <v>13</v>
       </c>
@@ -12465,7 +12468,7 @@
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A293" s="77"/>
+      <c r="A293" s="70"/>
       <c r="B293" s="9" t="s">
         <v>14</v>
       </c>
@@ -12500,60 +12503,181 @@
         <v>89975.487754523405</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="78"/>
-      <c r="B294" s="68" t="s">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A294" s="71"/>
+      <c r="B294" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C294" s="64">
+      <c r="C294" s="29">
         <v>167922.34111406258</v>
       </c>
-      <c r="D294" s="18">
+      <c r="D294" s="16">
         <v>134942.63117084559</v>
       </c>
-      <c r="E294" s="65">
+      <c r="E294" s="26">
         <v>74598.587639209611</v>
       </c>
-      <c r="F294" s="18">
+      <c r="F294" s="16">
         <v>64378.556744149617</v>
       </c>
-      <c r="G294" s="65">
+      <c r="G294" s="26">
         <v>154773.06702102642</v>
       </c>
-      <c r="H294" s="18">
+      <c r="H294" s="16">
         <v>203271.10914041701</v>
       </c>
-      <c r="I294" s="65">
+      <c r="I294" s="26">
         <v>285248.19531023491</v>
       </c>
-      <c r="J294" s="18">
+      <c r="J294" s="16">
         <v>109361.35804858152</v>
       </c>
-      <c r="K294" s="66">
+      <c r="K294" s="38">
         <v>245282.61438411221</v>
       </c>
-      <c r="L294" s="67">
+      <c r="L294" s="39">
         <v>91781.090163399771</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A295" s="5" t="s">
+      <c r="A295" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C295" s="27">
+        <v>147721.76516789402</v>
+      </c>
+      <c r="D295" s="13">
+        <v>128609.27545546243</v>
+      </c>
+      <c r="E295" s="21">
+        <v>56511.251433554273</v>
+      </c>
+      <c r="F295" s="13">
+        <v>48663.847536097244</v>
+      </c>
+      <c r="G295" s="21">
+        <v>204014.80203056446</v>
+      </c>
+      <c r="H295" s="13">
+        <v>171494.99213267674</v>
+      </c>
+      <c r="I295" s="21">
+        <v>108835.45615986057</v>
+      </c>
+      <c r="J295" s="13">
+        <v>86832.637728990507</v>
+      </c>
+      <c r="K295" s="36">
+        <v>168888.418984002</v>
+      </c>
+      <c r="L295" s="35">
+        <v>64340.510383125489</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A296" s="70"/>
+      <c r="B296" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C296" s="27">
+        <v>148491.92237802019</v>
+      </c>
+      <c r="D296" s="13">
+        <v>113675.67871337726</v>
+      </c>
+      <c r="E296" s="21">
+        <v>50529.626416058243</v>
+      </c>
+      <c r="F296" s="13">
+        <v>64542.567344349976</v>
+      </c>
+      <c r="G296" s="21">
+        <v>136863.8426433526</v>
+      </c>
+      <c r="H296" s="13">
+        <v>195869.8884491442</v>
+      </c>
+      <c r="I296" s="21">
+        <v>255355.00536047283</v>
+      </c>
+      <c r="J296" s="13">
+        <v>97854.223122844094</v>
+      </c>
+      <c r="K296" s="36">
+        <v>202969.26231862631</v>
+      </c>
+      <c r="L296" s="35">
+        <v>59859.578592527971</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="81"/>
+      <c r="B297" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C297" s="64">
+        <v>150395.25533946371</v>
+      </c>
+      <c r="D297" s="18">
+        <v>140677.75010637753</v>
+      </c>
+      <c r="E297" s="65">
+        <v>49135.030650538538</v>
+      </c>
+      <c r="F297" s="18">
+        <v>63207.424018143116</v>
+      </c>
+      <c r="G297" s="65">
+        <v>168845.53419127228</v>
+      </c>
+      <c r="H297" s="18">
+        <v>157960.13333206341</v>
+      </c>
+      <c r="I297" s="65">
+        <v>268817.6165882998</v>
+      </c>
+      <c r="J297" s="18">
+        <v>86904.256273700666</v>
+      </c>
+      <c r="K297" s="66">
+        <v>178814.61851066299</v>
+      </c>
+      <c r="L297" s="67">
+        <v>53351.77086467755</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A298" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A296" s="5" t="s">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A299" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A297" s="6" t="s">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A300" s="6" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="A283:A294"/>
+    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A43:A54"/>
+    <mergeCell ref="A55:A66"/>
+    <mergeCell ref="A67:A78"/>
+    <mergeCell ref="A19:A30"/>
+    <mergeCell ref="A31:A42"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A6"/>
     <mergeCell ref="A271:A282"/>
     <mergeCell ref="A259:A270"/>
     <mergeCell ref="A79:A90"/>
@@ -12567,16 +12691,6 @@
     <mergeCell ref="A163:A174"/>
     <mergeCell ref="A139:A150"/>
     <mergeCell ref="A103:A114"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A43:A54"/>
-    <mergeCell ref="A55:A66"/>
-    <mergeCell ref="A67:A78"/>
-    <mergeCell ref="A19:A30"/>
-    <mergeCell ref="A31:A42"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12639,7 +12753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48" t="s">
         <v>36</v>
       </c>
@@ -12655,7 +12769,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="51" t="s">
         <v>38</v>
       </c>
@@ -12671,7 +12785,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53" t="s">
         <v>40</v>
       </c>
